--- a/docs/import/sample-row-errors.xlsx
+++ b/docs/import/sample-row-errors.xlsx
@@ -31,7 +31,7 @@
     <t>توضیح</t>
   </si>
   <si>
-    <t>00GUMQX</t>
+    <t>00WZBTW</t>
   </si>
   <si>
     <t>خطا</t>
@@ -55,7 +55,7 @@
     <t>کد کالا در فایل عددی ذخیره شده بود و ممکن است صفرهای ابتدایی‌اش حذف شده باشد؛ قالب ستون را «متن» کنید.</t>
   </si>
   <si>
-    <t>CUR-MUTGUMQX</t>
+    <t>CUR-MUTWZBTW</t>
   </si>
   <si>
     <t>ارز پایه</t>
@@ -76,7 +76,7 @@
     <t>برای این مبلغ، ارز پایه را هم وارد کنید.</t>
   </si>
   <si>
-    <t>QTY-MUTGUMQX</t>
+    <t>QTY-MUTWZBTW</t>
   </si>
   <si>
     <t>موجودی فیزیکی</t>
@@ -88,7 +88,7 @@
     <t>فقط عدد صحیح مجاز است.</t>
   </si>
   <si>
-    <t>NEG-MUTGUMQX</t>
+    <t>NEG-MUTWZBTW</t>
   </si>
   <si>
     <t>NEGATIVE_NOT_ALLOWED</t>
@@ -97,7 +97,7 @@
     <t>عدد منفی مجاز نیست.</t>
   </si>
   <si>
-    <t>CAT-MUTGUMQX</t>
+    <t>CAT-MUTWZBTW</t>
   </si>
   <si>
     <t>کد دسته</t>
@@ -109,7 +109,7 @@
     <t>این کد دسته در پنل ثبت نشده است.</t>
   </si>
   <si>
-    <t>FX-MUTGUMQX</t>
+    <t>FX-MUTWZBTW</t>
   </si>
   <si>
     <t>FORMULA_NOT_ALLOWED</t>

--- a/docs/import/sample-row-errors.xlsx
+++ b/docs/import/sample-row-errors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
   <si>
     <t>ردیف</t>
   </si>
@@ -19,6 +19,12 @@
     <t>کد کالا</t>
   </si>
   <si>
+    <t>شماره فنی</t>
+  </si>
+  <si>
+    <t>نام قطعه</t>
+  </si>
+  <si>
     <t>نوع</t>
   </si>
   <si>
@@ -31,7 +37,16 @@
     <t>توضیح</t>
   </si>
   <si>
-    <t>00WZBTW</t>
+    <t>جزئیات</t>
+  </si>
+  <si>
+    <t>00W1U60</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>قطعهٔ واردشده آزمایشی</t>
   </si>
   <si>
     <t>خطا</t>
@@ -43,9 +58,15 @@
     <t>این کد کالا بیش از یک بار در فایل آمده است.</t>
   </si>
   <si>
+    <t>ردیف تکراری</t>
+  </si>
+  <si>
     <t>77001</t>
   </si>
   <si>
+    <t>کد عددی</t>
+  </si>
+  <si>
     <t>هشدار</t>
   </si>
   <si>
@@ -55,16 +76,16 @@
     <t>کد کالا در فایل عددی ذخیره شده بود و ممکن است صفرهای ابتدایی‌اش حذف شده باشد؛ قالب ستون را «متن» کنید.</t>
   </si>
   <si>
-    <t>CUR-MUTWZBTW</t>
+    <t>CUR-MV3W1U60</t>
   </si>
   <si>
     <t>ارز پایه</t>
   </si>
   <si>
-    <t>UNKNOWN_CURRENCY</t>
-  </si>
-  <si>
-    <t>ارز فقط IRR (ریال) یا AED (درهم) است؛ تومان پذیرفته نمی‌شود.</t>
+    <t>TOMAN_NEEDS_CONVERSION</t>
+  </si>
+  <si>
+    <t>ارز این ردیف تومان است. تومان فقط وقتی پذیرفته می‌شود که واحد قیمت را «تومان، تبدیل به ریال» انتخاب کنید.</t>
   </si>
   <si>
     <t>قیمت پایه</t>
@@ -73,10 +94,10 @@
     <t>CURRENCY_REQUIRED</t>
   </si>
   <si>
-    <t>برای این مبلغ، ارز پایه را هم وارد کنید.</t>
-  </si>
-  <si>
-    <t>QTY-MUTWZBTW</t>
+    <t>واحد این مبلغ مشخص نیست؛ واحد قیمت را در مرحلهٔ تطبیق ستون‌ها انتخاب کنید یا ستون ارز داشته باشید.</t>
+  </si>
+  <si>
+    <t>QTY-MV3W1U60</t>
   </si>
   <si>
     <t>موجودی فیزیکی</t>
@@ -88,7 +109,7 @@
     <t>فقط عدد صحیح مجاز است.</t>
   </si>
   <si>
-    <t>NEG-MUTWZBTW</t>
+    <t>NEG-MV3W1U60</t>
   </si>
   <si>
     <t>NEGATIVE_NOT_ALLOWED</t>
@@ -97,7 +118,7 @@
     <t>عدد منفی مجاز نیست.</t>
   </si>
   <si>
-    <t>CAT-MUTWZBTW</t>
+    <t>CAT-MV3W1U60</t>
   </si>
   <si>
     <t>کد دسته</t>
@@ -106,10 +127,10 @@
     <t>UNKNOWN_CATEGORY</t>
   </si>
   <si>
-    <t>این کد دسته در پنل ثبت نشده است.</t>
-  </si>
-  <si>
-    <t>FX-MUTWZBTW</t>
+    <t>این دسته در پنل ثبت نشده است؛ کد یا نام دسته را همان‌طور که در پنل است بنویسید.</t>
+  </si>
+  <si>
+    <t>FX-MV3W1U60</t>
   </si>
   <si>
     <t>FORMULA_NOT_ALLOWED</t>
@@ -498,23 +519,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="2" max="3" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="8" max="8" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -526,185 +546,275 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/import/sample-row-errors.xlsx
+++ b/docs/import/sample-row-errors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
   <si>
     <t>ردیف</t>
   </si>
@@ -40,7 +40,7 @@
     <t>جزئیات</t>
   </si>
   <si>
-    <t>00W1U60</t>
+    <t>002NXD3</t>
   </si>
   <si>
     <t/>
@@ -76,7 +76,7 @@
     <t>کد کالا در فایل عددی ذخیره شده بود و ممکن است صفرهای ابتدایی‌اش حذف شده باشد؛ قالب ستون را «متن» کنید.</t>
   </si>
   <si>
-    <t>CUR-MV3W1U60</t>
+    <t>CUR-MV92NXD3</t>
   </si>
   <si>
     <t>ارز پایه</t>
@@ -97,7 +97,7 @@
     <t>واحد این مبلغ مشخص نیست؛ واحد قیمت را در مرحلهٔ تطبیق ستون‌ها انتخاب کنید یا ستون ارز داشته باشید.</t>
   </si>
   <si>
-    <t>QTY-MV3W1U60</t>
+    <t>QTY-MV92NXD3</t>
   </si>
   <si>
     <t>موجودی فیزیکی</t>
@@ -106,10 +106,13 @@
     <t>NOT_A_WHOLE_NUMBER</t>
   </si>
   <si>
-    <t>فقط عدد صحیح مجاز است.</t>
-  </si>
-  <si>
-    <t>NEG-MV3W1U60</t>
+    <t>واحد این کالا اعشار نمی‌پذیرد؛ فقط عدد صحیح مجاز است (واحد در توضیح).</t>
+  </si>
+  <si>
+    <t>عدد</t>
+  </si>
+  <si>
+    <t>NEG-MV92NXD3</t>
   </si>
   <si>
     <t>NEGATIVE_NOT_ALLOWED</t>
@@ -118,7 +121,7 @@
     <t>عدد منفی مجاز نیست.</t>
   </si>
   <si>
-    <t>CAT-MV3W1U60</t>
+    <t>CAT-MV92NXD3</t>
   </si>
   <si>
     <t>کد دسته</t>
@@ -130,7 +133,7 @@
     <t>این دسته در پنل ثبت نشده است؛ کد یا نام دسته را همان‌طور که در پنل است بنویسید.</t>
   </si>
   <si>
-    <t>FX-MV3W1U60</t>
+    <t>FX-MV92NXD3</t>
   </si>
   <si>
     <t>FORMULA_NOT_ALLOWED</t>
@@ -727,7 +730,7 @@
         <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -735,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
@@ -750,10 +753,10 @@
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
@@ -764,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
@@ -776,13 +779,13 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
         <v>10</v>
@@ -793,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
@@ -808,10 +811,10 @@
         <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10" t="s">
         <v>10</v>

--- a/docs/import/sample-row-errors.xlsx
+++ b/docs/import/sample-row-errors.xlsx
@@ -40,7 +40,7 @@
     <t>جزئیات</t>
   </si>
   <si>
-    <t>002NXD3</t>
+    <t>00CJIQT</t>
   </si>
   <si>
     <t/>
@@ -76,7 +76,7 @@
     <t>کد کالا در فایل عددی ذخیره شده بود و ممکن است صفرهای ابتدایی‌اش حذف شده باشد؛ قالب ستون را «متن» کنید.</t>
   </si>
   <si>
-    <t>CUR-MV92NXD3</t>
+    <t>CUR-MVDCJIQT</t>
   </si>
   <si>
     <t>ارز پایه</t>
@@ -97,7 +97,7 @@
     <t>واحد این مبلغ مشخص نیست؛ واحد قیمت را در مرحلهٔ تطبیق ستون‌ها انتخاب کنید یا ستون ارز داشته باشید.</t>
   </si>
   <si>
-    <t>QTY-MV92NXD3</t>
+    <t>QTY-MVDCJIQT</t>
   </si>
   <si>
     <t>موجودی فیزیکی</t>
@@ -112,7 +112,7 @@
     <t>عدد</t>
   </si>
   <si>
-    <t>NEG-MV92NXD3</t>
+    <t>NEG-MVDCJIQT</t>
   </si>
   <si>
     <t>NEGATIVE_NOT_ALLOWED</t>
@@ -121,7 +121,7 @@
     <t>عدد منفی مجاز نیست.</t>
   </si>
   <si>
-    <t>CAT-MV92NXD3</t>
+    <t>CAT-MVDCJIQT</t>
   </si>
   <si>
     <t>کد دسته</t>
@@ -133,7 +133,7 @@
     <t>این دسته در پنل ثبت نشده است؛ کد یا نام دسته را همان‌طور که در پنل است بنویسید.</t>
   </si>
   <si>
-    <t>FX-MV92NXD3</t>
+    <t>FX-MVDCJIQT</t>
   </si>
   <si>
     <t>FORMULA_NOT_ALLOWED</t>

--- a/docs/import/sample-row-errors.xlsx
+++ b/docs/import/sample-row-errors.xlsx
@@ -40,7 +40,7 @@
     <t>جزئیات</t>
   </si>
   <si>
-    <t>00CJIQT</t>
+    <t>00DTLGD</t>
   </si>
   <si>
     <t/>
@@ -76,7 +76,7 @@
     <t>کد کالا در فایل عددی ذخیره شده بود و ممکن است صفرهای ابتدایی‌اش حذف شده باشد؛ قالب ستون را «متن» کنید.</t>
   </si>
   <si>
-    <t>CUR-MVDCJIQT</t>
+    <t>CUR-MVDDTLGD</t>
   </si>
   <si>
     <t>ارز پایه</t>
@@ -97,7 +97,7 @@
     <t>واحد این مبلغ مشخص نیست؛ واحد قیمت را در مرحلهٔ تطبیق ستون‌ها انتخاب کنید یا ستون ارز داشته باشید.</t>
   </si>
   <si>
-    <t>QTY-MVDCJIQT</t>
+    <t>QTY-MVDDTLGD</t>
   </si>
   <si>
     <t>موجودی فیزیکی</t>
@@ -112,7 +112,7 @@
     <t>عدد</t>
   </si>
   <si>
-    <t>NEG-MVDCJIQT</t>
+    <t>NEG-MVDDTLGD</t>
   </si>
   <si>
     <t>NEGATIVE_NOT_ALLOWED</t>
@@ -121,7 +121,7 @@
     <t>عدد منفی مجاز نیست.</t>
   </si>
   <si>
-    <t>CAT-MVDCJIQT</t>
+    <t>CAT-MVDDTLGD</t>
   </si>
   <si>
     <t>کد دسته</t>
@@ -133,7 +133,7 @@
     <t>این دسته در پنل ثبت نشده است؛ کد یا نام دسته را همان‌طور که در پنل است بنویسید.</t>
   </si>
   <si>
-    <t>FX-MVDCJIQT</t>
+    <t>FX-MVDDTLGD</t>
   </si>
   <si>
     <t>FORMULA_NOT_ALLOWED</t>
